--- a/Template/SC/V02/Table/Public/Common_Datasheet_Config.xlsx
+++ b/Template/SC/V02/Table/Public/Common_Datasheet_Config.xlsx
@@ -4,7 +4,7 @@
   <fileVersion appName="xl" lastEdited="3" lowestEdited="5" rupBuild="9302"/>
   <workbookPr/>
   <bookViews>
-    <workbookView windowWidth="20430" windowHeight="8205"/>
+    <workbookView windowWidth="27945" windowHeight="12255" activeTab="2"/>
   </bookViews>
   <sheets>
     <sheet name="Table10" sheetId="20" r:id="rId1"/>
@@ -48,8 +48,8 @@
     <t>Center Decode</t>
   </si>
   <si>
-    <t>If "center decode" feature is enabled(C1), it can improve instance performance but increase area. There is one repair elements.\
-If "center decode" feature is disabled(C0), it can improve instance area but decrease performance. There is one repair elements.\
+    <t>If "center decode" feature is enabled(C1), it can improve instance performance but increase area. There is one repair element.\
+If "center decode" feature is disabled(C0), it can improve instance area but decrease performance. There is one repair element.\
 The Center decode of this version is always True.</t>
   </si>
   <si>
